--- a/data/trans_dic/IP44C$hipoteca_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,54</t>
+          <t>0,61; 2,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,1</t>
+          <t>0,91; 3,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,44</t>
+          <t>0,88; 2,44</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,43</t>
+          <t>0,51; 3,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,35</t>
+          <t>0,5; 2,58</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,02</t>
+          <t>0,57; 1,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,48</t>
+          <t>0,95; 2,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,96</t>
+          <t>0,91; 1,98</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6050</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8842</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14892</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2771; 11238</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4599; 16254</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>8404; 23245</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1057</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2806</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3863</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3686</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>921; 6351</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1650; 8508</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11648</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18756</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3692; 12913</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7086; 18619</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12766; 27648</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$hipoteca_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Estudios-trans_dic.xlsx
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,49</t>
+          <t>0,59; 2,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,23</t>
+          <t>0,93; 3,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,44</t>
+          <t>0,97; 2,44</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,52</t>
+          <t>0,63; 3,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,58</t>
+          <t>0,48; 2,36</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,98</t>
+          <t>0,57; 2,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,5</t>
+          <t>0,89; 2,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,98</t>
+          <t>0,95; 2,0</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2771; 11238</t>
+          <t>2673; 12593</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4599; 16254</t>
+          <t>4666; 15619</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8404; 23245</t>
+          <t>9218; 23312</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3686</t>
+          <t>0; 3586</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>921; 6351</t>
+          <t>1130; 7169</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1650; 8508</t>
+          <t>1591; 7780</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3692; 12913</t>
+          <t>3708; 13012</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7086; 18619</t>
+          <t>6626; 17854</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12766; 27648</t>
+          <t>13303; 27969</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$hipoteca_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,79</t>
+          <t>0,91; 3,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,1</t>
+          <t>0,69; 2,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,44</t>
+          <t>1,06; 2,61</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,52; 3,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,98</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,36</t>
+          <t>0,52; 2,31</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,0</t>
+          <t>0,88; 2,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,4</t>
+          <t>0,6; 2,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,0</t>
+          <t>0,93; 2,07</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14892</t>
+          <t>14647</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2673; 12593</t>
+          <t>4233; 15290</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4666; 15619</t>
+          <t>2918; 12173</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9218; 23312</t>
+          <t>9391; 23131</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3599</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3586</t>
+          <t>854; 6098</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1130; 7169</t>
+          <t>0; 3171</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1591; 7780</t>
+          <t>1642; 7275</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>18245</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3708; 13012</t>
+          <t>6006; 17843</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6626; 17854</t>
+          <t>3722; 13270</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13303; 27969</t>
+          <t>12043; 26960</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$hipoteca_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,91; 3,3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,69; 2,88</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,06; 2,61</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,52; 3,69</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,12</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,52; 2,31</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,88; 2,61</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,6; 2,15</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,93; 2,07</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,70 +552,40 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -901,69 +595,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.01779402726767284</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.01516187835291734</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.01653736004466011</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>8236</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6411</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14647</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.009146822415981814</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.00689989027716047</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.01060317826801566</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>4233; 15290</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2918; 12173</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9391; 23131</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.03303503346787191</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.02878856014414473</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.02611717518406494</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +650,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.01621099539920661</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.006127200884958051</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.01142189358608429</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2682</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>917</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3599</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.005163444363766417</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.005212241768944854</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>854; 6098</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3171</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1642; 7275</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.03685977119513287</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.02119271236110561</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.02309142833527577</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +705,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.01598245970611355</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.01187869082558752</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.01403503507028383</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>10917</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7328</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18245</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.008792060614115627</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.006033139391511819</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.009263849270876739</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>6006; 17843</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>3722; 13270</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>12043; 26960</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.02612090653749811</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.02151036011415169</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.02073837530291405</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +769,364 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>8236</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>6411</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>14647</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>4233</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>2918</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>9391</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>15290</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>12173</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>23131</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2682</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>917</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>854</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>6098</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>3171</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>7275</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>10917</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>7328</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>18245</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>6006</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>3722</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>12043</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>17843</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>13270</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>26960</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>